--- a/site/StructureDefinition-hcen-submission-set-unique-id-identifier.xlsx
+++ b/site/StructureDefinition-hcen-submission-set-unique-id-identifier.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T01:23:13-03:00</t>
+    <t>2026-10-28T18:02:56-03:00</t>
   </si>
   <si>
     <t>Publisher</t>
